--- a/outputs/comment_task_flow_template/コメント・タスク進行表_テンプレート.xlsx
+++ b/outputs/comment_task_flow_template/コメント・タスク進行表_テンプレート.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\gameseisaku\GCCC2026_GroupB\outputs\comment_task_flow_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7F2BD6-378B-49C1-87EC-0B7AC9E1765A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA5E977-DAA2-413E-AA72-232166054F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="コメント・タスク表" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="174">
   <si>
     <t>コメント・タスク進行定義表</t>
   </si>
@@ -475,13 +475,6 @@
   </si>
   <si>
     <t>4</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>コメントの赤文字をクリックしてみて</t>
-    <rPh sb="5" eb="8">
-      <t>アカモジ</t>
-    </rPh>
     <phoneticPr fontId="5"/>
   </si>
   <si>
@@ -513,12 +506,543 @@
     </rPh>
     <phoneticPr fontId="5"/>
   </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>6</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>警備員から逃げながらタスクをこなして登録者を増やそう</t>
+    <rPh sb="0" eb="3">
+      <t>ケイビイン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ニ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>トウロクシャ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>コメントの赤文字をクリックしてみて右クリで閉じれるよ</t>
+    <rPh sb="5" eb="8">
+      <t>アカモジ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>自販機でドリンクを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>購入しよう</t>
+    </r>
+    <rPh sb="0" eb="3">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>がクリアされた後</t>
+    </r>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>ブッシュの中に隠れよう</t>
+    <rPh sb="5" eb="6">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カク</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <t>6,7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>はほぼ同タイミングで表示６出た後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <rPh sb="6" eb="7">
+      <t>ドウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>アト</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>6,7はほぼ同タイミングで表示６出た後7</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>7</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>自販機の使くでeを押すと購入できるよ</t>
+    <rPh sb="0" eb="3">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>６のタスクが選択されてからクリアされるまで</t>
+    <rPh sb="6" eb="8">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>６のタスクが選択されてからクリアされるまで</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>9</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>ドリンクを飲むと一定時間shiftダッシュが強化されるよ</t>
+    <rPh sb="5" eb="6">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>イッテイジカン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>コメント</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>ブッシュの近くでeを押すと隠れられるよ</t>
+    <rPh sb="5" eb="6">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カク</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>7のタスクが選択されてからクリアされるまで</t>
+    <rPh sb="6" eb="8">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>7のタスクが選択されてからクリアされるまで</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>11</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>ブッシュの中に隠れると敵の追跡から逃れられるよ</t>
+    <rPh sb="5" eb="6">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ツイセキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ノガ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>のタスクがクリアされたら</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>秒間表示</t>
+    </r>
+    <rPh sb="14" eb="16">
+      <t>ビョウカン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>7のタスクがクリアされたら</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>秒間表示</t>
+    </r>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>12</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>タスク</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>コーヒーカップに電気を灯そう</t>
+    <rPh sb="8" eb="10">
+      <t>デンキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>トモ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>7,6完了後</t>
+    <rPh sb="3" eb="6">
+      <t>カンリョウゴ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>13</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>コーヒーカップの近くでe押すとつくよ</t>
+    <rPh sb="8" eb="9">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>12のタスクが完了されるまで</t>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>e押して4秒後に点灯仕組みは自販機等と同じ</t>
+    <rPh sb="1" eb="2">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ビョウゴ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テントウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>ジハンキトウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>オナ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>14</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>城の電気を灯そう</t>
+    <rPh sb="0" eb="1">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>デンキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>トモ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>タスクが完了するとコーヒーカップを中心に半径</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を照らす</t>
+    </r>
+    <rPh sb="4" eb="6">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>チュウシン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ハンケイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>テ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>12完了後</t>
+    <rPh sb="2" eb="5">
+      <t>カンリョウゴ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>15</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>14後</t>
+    <rPh sb="2" eb="3">
+      <t>ゴ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>１４完了まで</t>
+    <rPh sb="2" eb="4">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>仕組みは同じく</t>
+    <rPh sb="0" eb="2">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オナ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>タスクが完了すると城を中心に半径</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を照らす</t>
+    </r>
+    <rPh sb="9" eb="10">
+      <t>シロ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>城の近くで</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>で点灯するよ</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>テントウ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -562,8 +1086,19 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -593,6 +1128,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF3F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -720,7 +1261,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -815,6 +1356,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -823,9 +1377,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1095,44 +1646,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.95" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
     </row>
     <row r="2" spans="1:16" ht="33.950000000000003" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="2"/>
@@ -1434,7 +1985,9 @@
       <c r="M10" s="16">
         <v>100</v>
       </c>
-      <c r="N10" s="15"/>
+      <c r="N10" s="15" t="s">
+        <v>131</v>
+      </c>
       <c r="O10" s="15"/>
       <c r="P10" s="17" t="s">
         <v>123</v>
@@ -1482,8 +2035,8 @@
       <c r="B12" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>129</v>
+      <c r="C12" s="33" t="s">
+        <v>134</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>118</v>
@@ -1500,22 +2053,30 @@
         <v>30</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K12" s="14"/>
       <c r="L12" s="14"/>
       <c r="M12" s="16"/>
       <c r="N12" s="15"/>
       <c r="O12" s="15"/>
-      <c r="P12" s="35" t="s">
+      <c r="P12" s="32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="27">
+      <c r="A13" s="13" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
+      <c r="B13" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>118</v>
+      </c>
       <c r="E13" s="15"/>
       <c r="F13" s="14"/>
       <c r="G13" s="15"/>
@@ -1527,66 +2088,128 @@
       <c r="M13" s="16"/>
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
-      <c r="P13" s="17"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
+      <c r="P13" s="17" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="28.5">
+      <c r="A14" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>118</v>
+      </c>
       <c r="E14" s="15"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="15"/>
+      <c r="F14" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>131</v>
+      </c>
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
       <c r="J14" s="14"/>
       <c r="K14" s="14"/>
       <c r="L14" s="14"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="15"/>
+      <c r="M14" s="16">
+        <v>100</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>145</v>
+      </c>
       <c r="O14" s="15"/>
-      <c r="P14" s="17"/>
+      <c r="P14" s="17" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
+      <c r="A15" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>118</v>
+      </c>
       <c r="E15" s="15"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="15"/>
+      <c r="F15" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>131</v>
+      </c>
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
       <c r="J15" s="14"/>
       <c r="K15" s="14"/>
       <c r="L15" s="14"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="15"/>
+      <c r="M15" s="16">
+        <v>100</v>
+      </c>
+      <c r="N15">
+        <v>11</v>
+      </c>
       <c r="O15" s="15"/>
-      <c r="P15" s="17"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
+      <c r="P15" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="40.5">
+      <c r="A16" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>118</v>
+      </c>
       <c r="E16" s="15"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="15"/>
+      <c r="F16" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>132</v>
+      </c>
       <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
+      <c r="I16" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J16" s="33" t="s">
+        <v>143</v>
+      </c>
       <c r="K16" s="14"/>
       <c r="L16" s="14"/>
       <c r="M16" s="16"/>
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
-      <c r="P16" s="17"/>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
+      <c r="P16" s="36" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="28.5">
+      <c r="A17" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>146</v>
+      </c>
       <c r="D17" s="14"/>
       <c r="E17" s="15"/>
       <c r="F17" s="14"/>
@@ -1599,30 +2222,54 @@
       <c r="M17" s="16"/>
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
-      <c r="P17" s="17"/>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
+      <c r="P17" s="17" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="42.75">
+      <c r="A18" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>149</v>
+      </c>
       <c r="D18" s="14"/>
       <c r="E18" s="15"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="15"/>
+      <c r="F18" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>140</v>
+      </c>
       <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
+      <c r="I18" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>150</v>
+      </c>
       <c r="K18" s="14"/>
       <c r="L18" s="14"/>
       <c r="M18" s="16"/>
       <c r="N18" s="15"/>
       <c r="O18" s="15"/>
-      <c r="P18" s="17"/>
-    </row>
-    <row r="19" spans="1:16">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
+      <c r="P18" s="17" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="27.75">
+      <c r="A19" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>153</v>
+      </c>
       <c r="D19" s="14"/>
       <c r="E19" s="15"/>
       <c r="F19" s="14"/>
@@ -1635,79 +2282,137 @@
       <c r="M19" s="16"/>
       <c r="N19" s="15"/>
       <c r="O19" s="15"/>
-      <c r="P19" s="17"/>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
+      <c r="P19" s="32" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="41.25">
+      <c r="A20" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B20" t="s">
+        <v>157</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>158</v>
+      </c>
       <c r="D20" s="14"/>
       <c r="E20" s="15"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="15"/>
+      <c r="F20" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>159</v>
+      </c>
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
       <c r="J20" s="14"/>
       <c r="K20" s="14"/>
       <c r="L20" s="14"/>
-      <c r="M20" s="16"/>
+      <c r="M20" s="16">
+        <v>500</v>
+      </c>
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
-      <c r="P20" s="17"/>
-    </row>
-    <row r="21" spans="1:16">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
+      <c r="P20" s="32" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="28.5">
+      <c r="A21" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>161</v>
+      </c>
       <c r="D21" s="14"/>
       <c r="E21" s="15"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="15"/>
+      <c r="F21" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>156</v>
+      </c>
       <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
+      <c r="I21" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J21" s="33" t="s">
+        <v>162</v>
+      </c>
       <c r="K21" s="14"/>
       <c r="L21" s="14"/>
       <c r="M21" s="16"/>
       <c r="N21" s="15"/>
       <c r="O21" s="15"/>
-      <c r="P21" s="17"/>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
+      <c r="P21" s="17" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="27.75">
+      <c r="A22" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>165</v>
+      </c>
       <c r="D22" s="14"/>
       <c r="E22" s="15"/>
       <c r="F22" s="14"/>
-      <c r="G22" s="15"/>
+      <c r="G22" s="15" t="s">
+        <v>167</v>
+      </c>
       <c r="H22" s="14"/>
       <c r="I22" s="14"/>
       <c r="J22" s="14"/>
       <c r="K22" s="14"/>
       <c r="L22" s="14"/>
-      <c r="M22" s="16"/>
+      <c r="M22" s="16">
+        <v>1000</v>
+      </c>
       <c r="N22" s="15"/>
       <c r="O22" s="15"/>
-      <c r="P22" s="17"/>
+      <c r="P22" s="32" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
+      <c r="A23" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>173</v>
+      </c>
       <c r="D23" s="14"/>
       <c r="E23" s="15"/>
       <c r="F23" s="14"/>
-      <c r="G23" s="15"/>
+      <c r="G23" s="15" t="s">
+        <v>169</v>
+      </c>
       <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
+      <c r="I23" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>170</v>
+      </c>
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
       <c r="M23" s="16"/>
       <c r="N23" s="15"/>
       <c r="O23" s="15"/>
-      <c r="P23" s="17"/>
+      <c r="P23" s="17" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="24" spans="1:16">
       <c r="A24" s="13"/>
@@ -3174,9 +3879,6 @@
   </mergeCells>
   <phoneticPr fontId="5"/>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="B5:B104" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"コメント,タスク"</formula1>
-    </dataValidation>
     <dataValidation type="list" sqref="F5:F104" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"これの後,対象付近に来た時,タスク開始時,タスク達成時,タスク失敗時,同時,手動"</formula1>
     </dataValidation>
@@ -3185,6 +3887,9 @@
     </dataValidation>
     <dataValidation type="list" sqref="K5:K104" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"なし,出現,追跡開始,攻撃開始,指定数撃破,全滅,逃走,消滅,停止"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="B5:B19 B21:B104" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"コメント,タスク"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3480,14 +4185,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2"/>

--- a/outputs/comment_task_flow_template/コメント・タスク進行表_テンプレート.xlsx
+++ b/outputs/comment_task_flow_template/コメント・タスク進行表_テンプレート.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\gameseisaku\GCCC2026_GroupB\outputs\comment_task_flow_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA5E977-DAA2-413E-AA72-232166054F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC13939E-2E9F-44C2-B910-969DCC83F79C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="177">
   <si>
     <t>コメント・タスク進行定義表</t>
   </si>
@@ -1034,6 +1034,27 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>テントウ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>16</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>脱出せよ</t>
+    <rPh sb="0" eb="2">
+      <t>ダッシュツ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>このタスクが始まるとゴールが解放される</t>
+    <rPh sb="6" eb="7">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイホウ</t>
     </rPh>
     <phoneticPr fontId="5"/>
   </si>
@@ -2414,23 +2435,37 @@
         <v>171</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
+    <row r="24" spans="1:16" ht="28.5">
+      <c r="A24" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>175</v>
+      </c>
       <c r="D24" s="14"/>
       <c r="E24" s="15"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="15"/>
+      <c r="F24" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>168</v>
+      </c>
       <c r="H24" s="14"/>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
-      <c r="M24" s="16"/>
+      <c r="M24" s="16">
+        <v>0</v>
+      </c>
       <c r="N24" s="15"/>
       <c r="O24" s="15"/>
-      <c r="P24" s="17"/>
+      <c r="P24" s="17" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="25" spans="1:16">
       <c r="A25" s="13"/>
